--- a/Finalisation-concertation/ig/PN13-FHIR-prescmed-medicationnoncompound-conceptmap.xlsx
+++ b/Finalisation-concertation/ig/PN13-FHIR-prescmed-medicationnoncompound-conceptmap.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T12:36:59+00:00</t>
+    <t>2026-05-21T12:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/Finalisation-concertation/ig/PN13-FHIR-prescmed-medicationnoncompound-conceptmap.xlsx
+++ b/Finalisation-concertation/ig/PN13-FHIR-prescmed-medicationnoncompound-conceptmap.xlsx
@@ -36,7 +36,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/medication/ConceptMap/PN13-FHIR-prescmed-medicationnoncompound-conceptmap</t>
+    <t>https://hl7.fr/ig/fhir/analyse-pharma/ConceptMap/PN13-FHIR-prescmed-medicationnoncompound-conceptmap</t>
   </si>
   <si>
     <t>Version</t>
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T12:38:31+00:00</t>
+    <t>2026-05-21T13:21:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,7 +111,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/medication/StructureDefinition/fr-medication-noncompound</t>
+    <t>https://hl7.fr/ig/fhir/analyse-pharma/StructureDefinition/fr-medication-noncompound</t>
   </si>
   <si>
     <t>Display</t>
